--- a/diseases/d092/2010-2014.xlsx
+++ b/diseases/d092/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>346</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>6.451191284254124</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>55</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>17.2870083417673</v>
       </c>
@@ -2193,9 +2187,6 @@
       <c r="O9" t="n">
         <v>75</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>1.534005213981455</v>
       </c>
@@ -2737,9 +2728,6 @@
       <c r="O12" t="n">
         <v>286</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>5.332487593343004</v>
       </c>
@@ -3372,9 +3360,6 @@
       <c r="O15" t="n">
         <v>99</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>2.024886882455521</v>
       </c>
@@ -3916,9 +3901,6 @@
       <c r="O18" t="n">
         <v>294</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>5.481648085464487</v>
       </c>
@@ -4551,9 +4533,6 @@
       <c r="O21" t="n">
         <v>101</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>2.065793688161693</v>
       </c>
@@ -5095,9 +5074,6 @@
       <c r="O24" t="n">
         <v>236</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>4.400234517583738</v>
       </c>
@@ -5730,9 +5706,6 @@
       <c r="O27" t="n">
         <v>126</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>2.577128759488845</v>
       </c>
@@ -6274,9 +6247,6 @@
       <c r="O30" t="n">
         <v>222</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>4.139203656371143</v>
       </c>
@@ -6909,9 +6879,6 @@
       <c r="O33" t="n">
         <v>138</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>2.822569593725878</v>
       </c>
@@ -7453,9 +7420,6 @@
       <c r="O36" t="n">
         <v>423</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>7.886861020923395</v>
       </c>
@@ -8088,9 +8052,6 @@
       <c r="O39" t="n">
         <v>241</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>4.929270087593743</v>
       </c>
@@ -8632,9 +8593,6 @@
       <c r="O42" t="n">
         <v>628</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>11.70909863153639</v>
       </c>
@@ -9267,9 +9225,6 @@
       <c r="O45" t="n">
         <v>466</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>9.531285729538109</v>
       </c>
@@ -9811,9 +9766,6 @@
       <c r="O48" t="n">
         <v>484</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>9.0242097733497</v>
       </c>
@@ -10446,9 +10398,6 @@
       <c r="O51" t="n">
         <v>596</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>12.1902281004393</v>
       </c>
@@ -10990,9 +10939,6 @@
       <c r="O54" t="n">
         <v>306</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>5.705388823646711</v>
       </c>
@@ -11625,9 +11571,6 @@
       <c r="O57" t="n">
         <v>329</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>6.729169538665317</v>
       </c>
@@ -12169,9 +12112,6 @@
       <c r="O60" t="n">
         <v>273</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>5.090101793645595</v>
       </c>
@@ -12804,9 +12744,6 @@
       <c r="O63" t="n">
         <v>234</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>4.78609626762214</v>
       </c>
@@ -13348,9 +13285,6 @@
       <c r="O66" t="n">
         <v>249</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>4.642620317281147</v>
       </c>
@@ -13983,9 +13917,6 @@
       <c r="O69" t="n">
         <v>185</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>3.783879527820923</v>
       </c>
@@ -14527,9 +14458,6 @@
       <c r="O72" t="n">
         <v>206</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>3.840882672128178</v>
       </c>
@@ -15162,9 +15090,6 @@
       <c r="O75" t="n">
         <v>91</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.861259659630832</v>
       </c>
@@ -15706,9 +15631,6 @@
       <c r="O78" t="n">
         <v>320</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>5.938858339855251</v>
       </c>
@@ -16102,9 +16024,6 @@
       <c r="O80" t="n">
         <v>123</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>38.54144144991022</v>
       </c>
@@ -16986,9 +16905,6 @@
       <c r="O84" t="n">
         <v>100</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>2.018991441091483</v>
       </c>
@@ -17530,9 +17446,6 @@
       <c r="O87" t="n">
         <v>279</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>5.177942115061297</v>
       </c>
@@ -18165,9 +18078,6 @@
       <c r="O90" t="n">
         <v>83</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.675762896105931</v>
       </c>
@@ -18709,9 +18619,6 @@
       <c r="O93" t="n">
         <v>297</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>5.512002896678155</v>
       </c>
@@ -19344,9 +19251,6 @@
       <c r="O96" t="n">
         <v>133</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>2.685258616651672</v>
       </c>
@@ -19888,9 +19792,6 @@
       <c r="O99" t="n">
         <v>314</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>5.827504745982965</v>
       </c>
@@ -20523,9 +20424,6 @@
       <c r="O102" t="n">
         <v>152</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>3.068866990459054</v>
       </c>
@@ -21067,9 +20965,6 @@
       <c r="O105" t="n">
         <v>370</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>6.866804955457634</v>
       </c>
@@ -21702,9 +21597,6 @@
       <c r="O108" t="n">
         <v>201</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>4.058172796593881</v>
       </c>
@@ -22246,9 +22138,6 @@
       <c r="O111" t="n">
         <v>388</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>7.200865737074492</v>
       </c>
@@ -22881,9 +22770,6 @@
       <c r="O114" t="n">
         <v>442</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>8.923942169624354</v>
       </c>
@@ -23425,9 +23311,6 @@
       <c r="O117" t="n">
         <v>597</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>11.07968259029245</v>
       </c>
@@ -24060,9 +23943,6 @@
       <c r="O120" t="n">
         <v>560</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>11.3063520701123</v>
       </c>
@@ -24604,9 +24484,6 @@
       <c r="O123" t="n">
         <v>517</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>9.59496800532864</v>
       </c>
@@ -25239,9 +25116,6 @@
       <c r="O126" t="n">
         <v>505</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>10.19590677751199</v>
       </c>
@@ -25783,9 +25657,6 @@
       <c r="O129" t="n">
         <v>348</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>6.458508444592586</v>
       </c>
@@ -26418,9 +26289,6 @@
       <c r="O132" t="n">
         <v>301</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>6.077164237685364</v>
       </c>
@@ -26962,9 +26830,6 @@
       <c r="O135" t="n">
         <v>336</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>6.235801256848014</v>
       </c>
@@ -27597,9 +27462,6 @@
       <c r="O138" t="n">
         <v>230</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>4.64368031451041</v>
       </c>
@@ -28141,9 +28003,6 @@
       <c r="O141" t="n">
         <v>245</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>4.546938416451677</v>
       </c>
@@ -28776,9 +28635,6 @@
       <c r="O144" t="n">
         <v>168</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>3.391905621033692</v>
       </c>
@@ -29320,9 +29176,6 @@
       <c r="O147" t="n">
         <v>254</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>4.713968807260105</v>
       </c>
@@ -29955,9 +29808,6 @@
       <c r="O150" t="n">
         <v>129</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>2.604498959008013</v>
       </c>
@@ -30499,9 +30349,6 @@
       <c r="O153" t="n">
         <v>346</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>6.390872209061315</v>
       </c>
@@ -30895,9 +30742,6 @@
       <c r="O155" t="n">
         <v>66</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>20.57096906406766</v>
       </c>
@@ -31779,9 +31623,6 @@
       <c r="O159" t="n">
         <v>137</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>2.729922491124015</v>
       </c>
@@ -32323,9 +32164,6 @@
       <c r="O162" t="n">
         <v>245</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>4.525328587341105</v>
       </c>
@@ -32958,9 +32796,6 @@
       <c r="O165" t="n">
         <v>113</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>2.251687894138787</v>
       </c>
@@ -33502,9 +33337,6 @@
       <c r="O168" t="n">
         <v>253</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>4.673094418764487</v>
       </c>
@@ -34137,9 +33969,6 @@
       <c r="O171" t="n">
         <v>122</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>2.431025868008247</v>
       </c>
@@ -34681,9 +34510,6 @@
       <c r="O174" t="n">
         <v>246</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>4.543799316269027</v>
       </c>
@@ -35316,9 +35142,6 @@
       <c r="O177" t="n">
         <v>108</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>2.152055686433531</v>
       </c>
@@ -35860,9 +35683,6 @@
       <c r="O180" t="n">
         <v>311</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>5.744396696584015</v>
       </c>
@@ -36495,9 +36315,6 @@
       <c r="O183" t="n">
         <v>164</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>3.267936412732399</v>
       </c>
@@ -37039,9 +36856,6 @@
       <c r="O186" t="n">
         <v>358</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>6.612520956196389</v>
       </c>
@@ -37674,9 +37488,6 @@
       <c r="O189" t="n">
         <v>272</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>5.419992099165929</v>
       </c>
@@ -38218,9 +38029,6 @@
       <c r="O192" t="n">
         <v>877</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>16.19882926978836</v>
       </c>
@@ -38853,9 +38661,6 @@
       <c r="O195" t="n">
         <v>570</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>11.35807167839919</v>
       </c>
@@ -39397,9 +39202,6 @@
       <c r="O198" t="n">
         <v>536</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>9.90031070536666</v>
       </c>
@@ -40032,9 +39834,6 @@
       <c r="O201" t="n">
         <v>530</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>10.56101401675714</v>
       </c>
@@ -40576,9 +40375,6 @@
       <c r="O204" t="n">
         <v>287</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>5.301099202313865</v>
       </c>
@@ -41211,9 +41007,6 @@
       <c r="O207" t="n">
         <v>274</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>5.459844982248031</v>
       </c>
@@ -41755,9 +41548,6 @@
       <c r="O210" t="n">
         <v>382</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>7.055818450466538</v>
       </c>
@@ -42390,9 +42180,6 @@
       <c r="O213" t="n">
         <v>383</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>7.631827110222613</v>
       </c>
@@ -42934,9 +42721,6 @@
       <c r="O216" t="n">
         <v>240</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>4.43297494270149</v>
       </c>
@@ -43569,9 +43353,6 @@
       <c r="O219" t="n">
         <v>192</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>3.825876775881833</v>
       </c>
@@ -44113,9 +43894,6 @@
       <c r="O222" t="n">
         <v>190</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>3.509438496305346</v>
       </c>
@@ -44748,9 +44526,6 @@
       <c r="O225" t="n">
         <v>68</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>1.354998024791482</v>
       </c>
@@ -45440,9 +45215,6 @@
       <c r="O229" t="n">
         <v>300</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>5.51566605436645</v>
       </c>
@@ -45836,9 +45608,6 @@
       <c r="O231" t="n">
         <v>101</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>31.18385972820642</v>
       </c>
@@ -46720,9 +46489,6 @@
       <c r="O235" t="n">
         <v>85</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>1.673187340192155</v>
       </c>
@@ -47412,9 +47178,6 @@
       <c r="O239" t="n">
         <v>210</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>3.860966238056515</v>
       </c>
@@ -48047,9 +47810,6 @@
       <c r="O242" t="n">
         <v>81</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>1.594449112418406</v>
       </c>
@@ -48739,9 +48499,6 @@
       <c r="O246" t="n">
         <v>205</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>3.769038470483741</v>
       </c>
@@ -49374,9 +49131,6 @@
       <c r="O249" t="n">
         <v>113</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>2.224354934608394</v>
       </c>
@@ -50066,9 +49820,6 @@
       <c r="O253" t="n">
         <v>243</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>4.467689504036824</v>
       </c>
@@ -50701,9 +50452,6 @@
       <c r="O256" t="n">
         <v>169</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>3.326690123440872</v>
       </c>
@@ -51393,9 +51141,6 @@
       <c r="O260" t="n">
         <v>274</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>5.037641662988024</v>
       </c>
@@ -52028,9 +51773,6 @@
       <c r="O263" t="n">
         <v>252</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>4.960508349746153</v>
       </c>
@@ -52720,9 +52462,6 @@
       <c r="O267" t="n">
         <v>353</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>6.490100390637855</v>
       </c>
@@ -53355,9 +53094,6 @@
       <c r="O270" t="n">
         <v>308</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>6.062843538578631</v>
       </c>
@@ -54047,9 +53783,6 @@
       <c r="O274" t="n">
         <v>659</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>12.11607976609163</v>
       </c>
@@ -54682,9 +54415,6 @@
       <c r="O277" t="n">
         <v>650</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>12.79496201323412</v>
       </c>
@@ -55374,9 +55104,6 @@
       <c r="O281" t="n">
         <v>474</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>8.71475236589899</v>
       </c>
@@ -56009,9 +55736,6 @@
       <c r="O284" t="n">
         <v>593</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>11.67294226745821</v>
       </c>
@@ -56701,9 +56425,6 @@
       <c r="O288" t="n">
         <v>386</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>7.096823656618165</v>
       </c>
@@ -57336,9 +57057,6 @@
       <c r="O291" t="n">
         <v>299</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>5.885682526087697</v>
       </c>
@@ -58028,9 +57746,6 @@
       <c r="O295" t="n">
         <v>414</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>7.611619155025701</v>
       </c>
@@ -58663,9 +58378,6 @@
       <c r="O298" t="n">
         <v>439</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>8.641520498168894</v>
       </c>
@@ -59355,9 +59067,6 @@
       <c r="O302" t="n">
         <v>332</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>6.104003766832204</v>
       </c>
@@ -59990,9 +59699,6 @@
       <c r="O305" t="n">
         <v>184</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>3.621958477592429</v>
       </c>
@@ -60682,9 +60388,6 @@
       <c r="O309" t="n">
         <v>211</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>3.87935179157107</v>
       </c>
@@ -61317,9 +61020,6 @@
       <c r="O312" t="n">
         <v>118</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>2.32277771932558</v>
       </c>
@@ -62009,9 +61709,6 @@
       <c r="O316" t="n">
         <v>346</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>6.335042452108177</v>
       </c>
@@ -62405,9 +62102,6 @@
       <c r="O318" t="n">
         <v>142</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>43.35712377390176</v>
       </c>
@@ -63289,9 +62983,6 @@
       <c r="O322" t="n">
         <v>130</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>2.53046534284399</v>
       </c>
@@ -63981,9 +63672,6 @@
       <c r="O326" t="n">
         <v>248</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>4.540724069719157</v>
       </c>
@@ -64616,9 +64304,6 @@
       <c r="O329" t="n">
         <v>95</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>1.8491862120783</v>
       </c>
@@ -65308,9 +64993,6 @@
       <c r="O333" t="n">
         <v>325</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>5.950545655881958</v>
       </c>
@@ -65943,9 +65625,6 @@
       <c r="O336" t="n">
         <v>153</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>2.978163057347157</v>
       </c>
@@ -66635,9 +66314,6 @@
       <c r="O340" t="n">
         <v>294</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>5.382955147167064</v>
       </c>
@@ -67270,9 +66946,6 @@
       <c r="O343" t="n">
         <v>164</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>3.192279355587803</v>
       </c>
@@ -67962,9 +67635,6 @@
       <c r="O347" t="n">
         <v>313</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>5.730833200895548</v>
       </c>
@@ -68597,9 +68267,6 @@
       <c r="O350" t="n">
         <v>267</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>5.197186511841118</v>
       </c>
@@ -69289,9 +68956,6 @@
       <c r="O354" t="n">
         <v>535</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>9.795513618144147</v>
       </c>
@@ -69924,9 +69588,6 @@
       <c r="O357" t="n">
         <v>342</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>6.657070363481881</v>
       </c>
@@ -70616,9 +70277,6 @@
       <c r="O361" t="n">
         <v>928</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>16.9910965189491</v>
       </c>
@@ -71251,9 +70909,6 @@
       <c r="O364" t="n">
         <v>843</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>16.40909449244218</v>
       </c>
@@ -71943,9 +71598,6 @@
       <c r="O368" t="n">
         <v>558</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>10.2166291568681</v>
       </c>
@@ -72578,9 +72230,6 @@
       <c r="O371" t="n">
         <v>631</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>12.28248947180429</v>
       </c>
@@ -73270,9 +72919,6 @@
       <c r="O375" t="n">
         <v>382</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>6.99417981706741</v>
       </c>
@@ -73905,9 +73551,6 @@
       <c r="O378" t="n">
         <v>392</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>7.630326264575724</v>
       </c>
@@ -74597,9 +74240,6 @@
       <c r="O382" t="n">
         <v>474</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>8.678641971963227</v>
       </c>
@@ -75232,9 +74872,6 @@
       <c r="O385" t="n">
         <v>360</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>7.007442487875664</v>
       </c>
@@ -75924,9 +75561,6 @@
       <c r="O389" t="n">
         <v>266</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>4.870292752198773</v>
       </c>
@@ -76559,9 +76193,6 @@
       <c r="O392" t="n">
         <v>224</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>4.360186436900414</v>
       </c>
@@ -77251,9 +76882,6 @@
       <c r="O396" t="n">
         <v>227</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>4.156227273492937</v>
       </c>
@@ -77885,9 +77513,6 @@
       </c>
       <c r="O399" t="n">
         <v>143</v>
-      </c>
-      <c r="Q399" t="n">
-        <v>0</v>
       </c>
       <c r="R399" t="n">
         <v>2.783511877128389</v>
